--- a/output/pdf_financials_xlsx/VCI.xlsx
+++ b/output/pdf_financials_xlsx/VCI.xlsx
@@ -987,22 +987,22 @@
         <v>1.146471</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>1.499813</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>1.941403</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>1.532615</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>1.775114</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>1.827324</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>2.316747</v>
       </c>
     </row>
     <row r="11">
@@ -1050,13 +1050,13 @@
         <v>2.404951</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>4.581614</v>
+        <v>3.081801</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>6.305065</v>
+        <v>4.363662</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>4.38117</v>
+        <v>2.848555</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>3.296708</v>
@@ -8641,10 +8641,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="P124" s="1" t="inlineStr">
         <is>
@@ -8712,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024</v>
       </c>
       <c r="P125" s="1" t="inlineStr">
         <is>
@@ -17830,7 +17830,11 @@
           <t>Lease payments (Note 7) $</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -26996,7 +27000,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -31372,7 +31376,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -34638,7 +34642,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -36612,7 +36616,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">

--- a/output/pdf_financials_xlsx/VCI.xlsx
+++ b/output/pdf_financials_xlsx/VCI.xlsx
@@ -7773,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -21344,7 +21344,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
